--- a/data/trans_orig/IP3104-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3104-Habitat-trans_orig.xlsx
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>6877</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17206</t>
+          <t>18113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>14516</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28304</t>
+          <t>27805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66828</t>
+          <t>66861</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85474</t>
+          <t>85296</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>82070</t>
+          <t>82263</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>100238</t>
+          <t>100339</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>153409</t>
+          <t>154537</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>180965</t>
+          <t>181307</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,24%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17349</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32492</t>
+          <t>31606</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32937</t>
+          <t>32742</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39575</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59180</t>
+          <t>59572</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21236</t>
+          <t>20837</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19871</t>
+          <t>20383</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20725</t>
+          <t>19850</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38307</t>
+          <t>36214</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>27167</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>22097</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>37260</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82160</t>
+          <t>82631</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103900</t>
+          <t>103097</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86889</t>
+          <t>87521</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108815</t>
+          <t>108471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>175484</t>
+          <t>176156</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206856</t>
+          <t>208097</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,11%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42404</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61776</t>
+          <t>62420</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49293</t>
+          <t>49499</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70321</t>
+          <t>70107</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97353</t>
+          <t>97921</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125569</t>
+          <t>127628</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14088</t>
+          <t>14053</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26922</t>
+          <t>27797</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14344</t>
+          <t>14366</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28482</t>
+          <t>27915</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>32088</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>51097</t>
+          <t>51227</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12647</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11032</t>
+          <t>9936</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>8317</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19503</t>
+          <t>19940</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67354</t>
+          <t>67242</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83428</t>
+          <t>83790</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>73405</t>
+          <t>73836</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>91146</t>
+          <t>91217</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>145815</t>
+          <t>144098</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>170386</t>
+          <t>170892</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>28171</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45221</t>
+          <t>44126</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33529</t>
+          <t>34213</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50940</t>
+          <t>51075</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>68290</t>
+          <t>67103</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>90804</t>
+          <t>91202</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>10899</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18587</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14508</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>19458</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>14475</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28947</t>
+          <t>28556</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>91307</t>
+          <t>91550</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>116240</t>
+          <t>116174</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>81563</t>
+          <t>80548</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>103423</t>
+          <t>103871</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>180170</t>
+          <t>179509</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>213233</t>
+          <t>213007</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48784</t>
+          <t>48639</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>71805</t>
+          <t>71993</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,47 +3472,47 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>24,75%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>36,64%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>57760</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>48151</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>69225</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>29,79%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>24,83%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>36,54%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>57760</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>47470</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>67851</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>29,79%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>24,48%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>102879</t>
+          <t>102841</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>131840</t>
+          <t>133634</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13474</t>
+          <t>13294</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27869</t>
+          <t>27978</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15350</t>
+          <t>16484</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29821</t>
+          <t>30331</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32929</t>
+          <t>31941</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53768</t>
+          <t>53113</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14593</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>21382</t>
+          <t>22088</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>27176</t>
+          <t>27842</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>45939</t>
+          <t>46836</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>36694</t>
+          <t>35743</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>58854</t>
+          <t>56583</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>68788</t>
+          <t>68835</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>97876</t>
+          <t>98296</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>328696</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>367802</t>
+          <t>368966</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4154,12 +4154,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>342361</t>
+          <t>343885</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>384464</t>
+          <t>384362</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>684148</t>
+          <t>685820</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>740291</t>
+          <t>743700</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -4252,12 +4252,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>153156</t>
+          <t>155419</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>190480</t>
+          <t>192224</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>166485</t>
+          <t>165616</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>204762</t>
+          <t>202131</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>333590</t>
+          <t>329670</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>383358</t>
+          <t>383276</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4365,12 +4365,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>50268</t>
+          <t>49516</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>74737</t>
+          <t>73136</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>49442</t>
+          <t>51764</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>74259</t>
+          <t>74403</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>106688</t>
+          <t>106302</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>139986</t>
+          <t>139851</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>19152</t>
+          <t>19058</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4493,49 +4493,49 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>13535</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>8418</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>20404</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
           <t>1,26%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>3,04%</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>13535</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>8724</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>20895</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>38</t>
@@ -4548,12 +4548,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>18544</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>35720</t>
+          <t>34228</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -5053,12 +5053,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>6572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17470</t>
+          <t>17807</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13440</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28611</t>
+          <t>28934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -5166,12 +5166,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61931</t>
+          <t>62206</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81629</t>
+          <t>80658</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54805</t>
+          <t>54755</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73862</t>
+          <t>74034</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>121514</t>
+          <t>122806</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>149521</t>
+          <t>151636</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>55,68%</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5279,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29848</t>
+          <t>30056</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47927</t>
+          <t>47146</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43347</t>
+          <t>44470</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62862</t>
+          <t>63105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78733</t>
+          <t>79145</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105463</t>
+          <t>106611</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,15%</t>
         </is>
       </c>
     </row>
@@ -5392,12 +5392,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12570</t>
+          <t>12387</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5407,12 +5407,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11128</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20536</t>
+          <t>19568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10348</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18539</t>
+          <t>18226</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -5848,12 +5848,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14915</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20941</t>
+          <t>21836</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>17254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32017</t>
+          <t>31875</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -5961,12 +5961,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80040</t>
+          <t>79792</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101405</t>
+          <t>100945</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5976,12 +5976,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93750</t>
+          <t>94253</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>116791</t>
+          <t>116671</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6011,12 +6011,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>178573</t>
+          <t>178367</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>210341</t>
+          <t>210222</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,95%</t>
         </is>
       </c>
     </row>
@@ -6074,12 +6074,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52294</t>
+          <t>51257</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72480</t>
+          <t>70731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49165</t>
+          <t>49119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68795</t>
+          <t>69801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>107180</t>
+          <t>106837</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135552</t>
+          <t>135928</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26316</t>
+          <t>26570</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>24435</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>28543</t>
+          <t>28501</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>46244</t>
+          <t>46456</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11640</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12919</t>
+          <t>12930</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20192</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -6643,12 +6643,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>12686</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6678,12 +6678,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6693,12 +6693,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6713,12 +6713,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23645</t>
+          <t>23800</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6728,12 +6728,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -6756,12 +6756,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74381</t>
+          <t>73684</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>92432</t>
+          <t>91779</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>72471</t>
+          <t>72152</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>91446</t>
+          <t>91477</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>150921</t>
+          <t>150194</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>176885</t>
+          <t>177158</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26427</t>
+          <t>26241</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42109</t>
+          <t>42514</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6904,12 +6904,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33327</t>
+          <t>32655</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50450</t>
+          <t>49547</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6939,12 +6939,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>64761</t>
+          <t>62965</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>88170</t>
+          <t>86876</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>18648</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>16289</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16525</t>
+          <t>16584</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30729</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -7095,12 +7095,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11619</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -7438,12 +7438,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7453,12 +7453,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7473,12 +7473,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19425</t>
+          <t>19071</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28534</t>
+          <t>27680</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -7551,12 +7551,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>73691</t>
+          <t>73459</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>95647</t>
+          <t>97567</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7566,12 +7566,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7586,12 +7586,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>83024</t>
+          <t>82464</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>106230</t>
+          <t>106516</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7621,12 +7621,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>162960</t>
+          <t>161351</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>194973</t>
+          <t>193611</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,12%</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>51364</t>
+          <t>51584</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>73121</t>
+          <t>72801</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7679,12 +7679,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7699,12 +7699,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>43261</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>65430</t>
+          <t>65551</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>100224</t>
+          <t>101929</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>131693</t>
+          <t>132651</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -7777,12 +7777,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>26990</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7812,12 +7812,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>16919</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31897</t>
+          <t>32485</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32518</t>
+          <t>32854</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54346</t>
+          <t>53812</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17495</t>
+          <t>17978</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7925,12 +7925,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7940,12 +7940,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7960,12 +7960,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>20835</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7975,12 +7975,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -8233,12 +8233,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>24501</t>
+          <t>24818</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>42377</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>37275</t>
+          <t>37564</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>58742</t>
+          <t>59614</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>66394</t>
+          <t>66490</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>94918</t>
+          <t>94797</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>309157</t>
+          <t>305178</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>350016</t>
+          <t>351202</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8361,12 +8361,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>324271</t>
+          <t>322471</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>367235</t>
+          <t>366465</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8396,12 +8396,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>644650</t>
+          <t>642111</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>704645</t>
+          <t>703335</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,36%</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>175899</t>
+          <t>176653</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>214555</t>
+          <t>215166</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>189191</t>
+          <t>188574</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>227800</t>
+          <t>228026</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8529,12 +8529,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>377210</t>
+          <t>374854</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>431317</t>
+          <t>432693</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -8572,12 +8572,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>46824</t>
+          <t>47074</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>70271</t>
+          <t>70924</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8587,12 +8587,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>46730</t>
+          <t>46945</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>70815</t>
+          <t>70392</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8642,12 +8642,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>99721</t>
+          <t>98811</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>133643</t>
+          <t>132453</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8657,12 +8657,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>18552</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>35391</t>
+          <t>35388</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -8720,12 +8720,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12805</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>26678</t>
+          <t>27422</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>34503</t>
+          <t>34976</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>55511</t>
+          <t>56892</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -9260,12 +9260,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>553</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9330,12 +9330,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2273</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29905</t>
+          <t>31587</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48290</t>
+          <t>49678</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>27513</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46992</t>
+          <t>46357</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63687</t>
+          <t>64475</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89813</t>
+          <t>89418</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -9486,12 +9486,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39608</t>
+          <t>40324</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58605</t>
+          <t>58806</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>53054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72733</t>
+          <t>73820</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99229</t>
+          <t>98071</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127177</t>
+          <t>125367</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>47,84%</t>
         </is>
       </c>
     </row>
@@ -9599,12 +9599,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>18182</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32095</t>
+          <t>33606</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>16267</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30580</t>
+          <t>31567</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38384</t>
+          <t>38295</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58089</t>
+          <t>59292</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -9712,12 +9712,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13752</t>
+          <t>13755</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -9747,12 +9747,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19531</t>
+          <t>19485</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9782,12 +9782,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>13689</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29585</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9797,12 +9797,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -10055,12 +10055,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5368</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14776</t>
+          <t>14925</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16738</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14276</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27905</t>
+          <t>27832</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -10168,12 +10168,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54499</t>
+          <t>54027</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74886</t>
+          <t>74336</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10183,12 +10183,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67302</t>
+          <t>68088</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90606</t>
+          <t>90074</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128575</t>
+          <t>128011</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157903</t>
+          <t>159042</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -10281,12 +10281,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60687</t>
+          <t>61020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81781</t>
+          <t>81012</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10316,12 +10316,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52418</t>
+          <t>52162</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>73629</t>
+          <t>72951</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10331,12 +10331,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10351,12 +10351,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119135</t>
+          <t>118821</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147754</t>
+          <t>150097</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10366,12 +10366,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -10394,12 +10394,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27349</t>
+          <t>27645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43544</t>
+          <t>44246</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10429,12 +10429,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29834</t>
+          <t>30876</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48342</t>
+          <t>49314</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10444,12 +10444,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10464,12 +10464,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>62454</t>
+          <t>61963</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>86993</t>
+          <t>86881</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10479,12 +10479,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -10507,12 +10507,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19154</t>
+          <t>19122</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10542,12 +10542,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24330</t>
+          <t>25550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10557,12 +10557,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10577,12 +10577,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22388</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38430</t>
+          <t>39000</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10592,12 +10592,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -10850,12 +10850,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2381</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10920,12 +10920,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11773</t>
+          <t>11566</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10935,12 +10935,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42441</t>
+          <t>43557</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60392</t>
+          <t>60813</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10998,12 +10998,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39055</t>
+          <t>39340</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57469</t>
+          <t>58486</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11013,12 +11013,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11033,12 +11033,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86852</t>
+          <t>86851</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112641</t>
+          <t>112153</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>35937</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54069</t>
+          <t>52589</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46781</t>
+          <t>48116</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>66922</t>
+          <t>68061</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11126,12 +11126,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11146,12 +11146,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>89524</t>
+          <t>90929</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>117171</t>
+          <t>116895</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11161,12 +11161,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -11189,12 +11189,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19340</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33463</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20896</t>
+          <t>20357</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37159</t>
+          <t>35701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11259,12 +11259,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42810</t>
+          <t>42837</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63941</t>
+          <t>63073</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -11302,12 +11302,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12796</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25072</t>
+          <t>24546</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11337,12 +11337,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29928</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11372,12 +11372,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31773</t>
+          <t>31656</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>49744</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11387,12 +11387,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -11645,12 +11645,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13248</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11660,12 +11660,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11680,12 +11680,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11695,12 +11695,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11715,12 +11715,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19601</t>
+          <t>18782</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11730,12 +11730,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -11758,12 +11758,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>75116</t>
+          <t>75620</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>98548</t>
+          <t>99920</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11773,12 +11773,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11793,12 +11793,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>75865</t>
+          <t>73431</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>98151</t>
+          <t>97371</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11808,12 +11808,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11828,12 +11828,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>157636</t>
+          <t>157482</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>189665</t>
+          <t>189197</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -11871,12 +11871,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>47663</t>
+          <t>48308</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>68920</t>
+          <t>69370</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11886,12 +11886,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11906,12 +11906,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>53402</t>
+          <t>54553</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>75877</t>
+          <t>77219</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11921,12 +11921,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11941,12 +11941,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>106096</t>
+          <t>109101</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>137868</t>
+          <t>139130</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11956,12 +11956,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -11984,12 +11984,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20326</t>
+          <t>19750</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35674</t>
+          <t>36084</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11999,12 +11999,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12019,12 +12019,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27664</t>
+          <t>27556</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12034,12 +12034,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12054,12 +12054,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>36891</t>
+          <t>36717</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>59279</t>
+          <t>58898</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12069,12 +12069,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -12097,12 +12097,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12112,12 +12112,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8531</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20999</t>
+          <t>20816</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>16632</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>31271</t>
+          <t>33628</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -12440,12 +12440,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>16672</t>
+          <t>17592</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>32066</t>
+          <t>33066</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12455,12 +12455,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12475,12 +12475,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>14375</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>28521</t>
+          <t>30165</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12490,12 +12490,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34006</t>
+          <t>34488</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>55396</t>
+          <t>54826</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12525,12 +12525,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -12553,12 +12553,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>222684</t>
+          <t>221998</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>262668</t>
+          <t>261939</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12588,12 +12588,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>228509</t>
+          <t>227770</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>272118</t>
+          <t>271195</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12603,12 +12603,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12623,12 +12623,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>465556</t>
+          <t>466295</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>524915</t>
+          <t>526996</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12638,12 +12638,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -12666,12 +12666,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>202773</t>
+          <t>201642</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>242683</t>
+          <t>242869</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12681,12 +12681,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12701,12 +12701,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>226649</t>
+          <t>226001</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>269096</t>
+          <t>267799</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12716,12 +12716,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>439239</t>
+          <t>442072</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>498004</t>
+          <t>499370</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12751,12 +12751,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -12779,12 +12779,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>97265</t>
+          <t>98586</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>128173</t>
+          <t>129892</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12794,12 +12794,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12814,12 +12814,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>94047</t>
+          <t>94350</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>125526</t>
+          <t>126515</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12849,12 +12849,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>200068</t>
+          <t>202340</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>244440</t>
+          <t>246259</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -12892,12 +12892,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>38858</t>
+          <t>38667</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>60833</t>
+          <t>60028</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12907,12 +12907,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12927,12 +12927,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>53336</t>
+          <t>53457</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>78418</t>
+          <t>79236</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>99564</t>
+          <t>99723</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>131815</t>
+          <t>130266</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -13359,7 +13359,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13394,7 +13394,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13424,12 +13424,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -13467,12 +13467,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>378</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13537,12 +13537,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>394</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -13580,12 +13580,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>39049</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56322</t>
+          <t>56319</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13595,12 +13595,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13615,12 +13615,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58826</t>
+          <t>56921</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>87203</t>
+          <t>86417</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13630,12 +13630,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13650,12 +13650,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>102172</t>
+          <t>101918</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>138949</t>
+          <t>138620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13665,12 +13665,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,21%</t>
         </is>
       </c>
     </row>
@@ -13693,12 +13693,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28774</t>
+          <t>28742</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44093</t>
+          <t>44261</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13708,12 +13708,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13728,12 +13728,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29623</t>
+          <t>29382</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51469</t>
+          <t>52630</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13763,12 +13763,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63992</t>
+          <t>64556</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91614</t>
+          <t>91951</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13778,12 +13778,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17114</t>
+          <t>17423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32046</t>
+          <t>32524</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13821,12 +13821,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -13841,12 +13841,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12846</t>
+          <t>12406</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28218</t>
+          <t>29690</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13856,12 +13856,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -13876,12 +13876,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33608</t>
+          <t>33723</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56102</t>
+          <t>56591</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -13891,12 +13891,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -13919,12 +13919,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -13934,12 +13934,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>498</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -13989,12 +13989,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14004,12 +14004,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -14149,12 +14149,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>780</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14164,12 +14164,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14219,12 +14219,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14234,12 +14234,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -14267,7 +14267,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14297,12 +14297,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14312,12 +14312,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14332,12 +14332,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>13408</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14347,12 +14347,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -14375,12 +14375,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52534</t>
+          <t>51636</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79296</t>
+          <t>77472</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14390,12 +14390,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14410,12 +14410,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44487</t>
+          <t>43843</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69332</t>
+          <t>69672</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14425,12 +14425,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14445,12 +14445,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100529</t>
+          <t>101461</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137718</t>
+          <t>138818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14460,12 +14460,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -14488,12 +14488,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58203</t>
+          <t>57961</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81881</t>
+          <t>81866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14503,12 +14503,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14523,12 +14523,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92376</t>
+          <t>92084</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122288</t>
+          <t>122096</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14558,12 +14558,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157996</t>
+          <t>158482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>197149</t>
+          <t>197483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14573,12 +14573,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,54%</t>
         </is>
       </c>
     </row>
@@ -14601,12 +14601,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29155</t>
+          <t>29042</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48332</t>
+          <t>48105</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -14616,12 +14616,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51334</t>
+          <t>50834</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79014</t>
+          <t>79547</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -14651,12 +14651,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14671,12 +14671,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>85883</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119171</t>
+          <t>122003</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -14686,12 +14686,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -14714,12 +14714,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16040</t>
+          <t>16418</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14729,12 +14729,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14749,12 +14749,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22312</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14764,12 +14764,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33521</t>
+          <t>35025</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14799,12 +14799,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -14944,12 +14944,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -14959,12 +14959,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -14979,12 +14979,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>383</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -14994,12 +14994,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15014,12 +15014,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11158</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15029,12 +15029,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -15057,12 +15057,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25262</t>
+          <t>24974</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15072,12 +15072,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15092,12 +15092,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14686</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30870</t>
+          <t>30353</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15107,12 +15107,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15127,12 +15127,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27193</t>
+          <t>27067</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51119</t>
+          <t>50051</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15142,12 +15142,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -15170,12 +15170,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40469</t>
+          <t>36709</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78834</t>
+          <t>78409</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15185,12 +15185,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46735</t>
+          <t>46439</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76729</t>
+          <t>75567</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92057</t>
+          <t>90195</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>143482</t>
+          <t>142634</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,41%</t>
         </is>
       </c>
     </row>
@@ -15283,12 +15283,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>26585</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57640</t>
+          <t>56971</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15298,12 +15298,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15318,12 +15318,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53515</t>
+          <t>51452</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>79898</t>
+          <t>78759</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15333,12 +15333,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15353,12 +15353,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>83684</t>
+          <t>83710</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>130639</t>
+          <t>128879</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15373,7 +15373,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -15396,12 +15396,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30240</t>
+          <t>30628</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104375</t>
+          <t>112447</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15411,12 +15411,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15431,12 +15431,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22507</t>
+          <t>22106</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42845</t>
+          <t>41434</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15446,12 +15446,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15466,12 +15466,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60805</t>
+          <t>61379</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>153740</t>
+          <t>161489</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15481,12 +15481,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -15509,12 +15509,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>11511</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15524,12 +15524,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15544,12 +15544,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>983</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15559,12 +15559,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15579,12 +15579,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17168</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15594,12 +15594,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -15739,12 +15739,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>6138</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15754,12 +15754,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15774,12 +15774,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>11339</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15789,12 +15789,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15809,12 +15809,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>14546</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15824,12 +15824,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -15852,12 +15852,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15867,12 +15867,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -15907,7 +15907,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -15922,12 +15922,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>16702</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -15937,12 +15937,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -15965,12 +15965,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45793</t>
+          <t>45311</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>65305</t>
+          <t>66266</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -15980,12 +15980,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -16000,12 +16000,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>52987</t>
+          <t>52981</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>75029</t>
+          <t>75301</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16020,7 +16020,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -16035,12 +16035,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>105382</t>
+          <t>103913</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>134694</t>
+          <t>134688</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16050,7 +16050,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -16078,12 +16078,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48680</t>
+          <t>47981</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>69275</t>
+          <t>69086</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16093,12 +16093,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16113,12 +16113,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>49086</t>
+          <t>49265</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>72283</t>
+          <t>70837</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16128,12 +16128,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16148,12 +16148,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>105191</t>
+          <t>103423</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>136313</t>
+          <t>132051</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16163,12 +16163,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -16191,12 +16191,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22719</t>
+          <t>22865</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41445</t>
+          <t>39909</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16206,12 +16206,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16226,12 +16226,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>32234</t>
+          <t>31944</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>51818</t>
+          <t>52135</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16241,12 +16241,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16261,12 +16261,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>58737</t>
+          <t>60967</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>85616</t>
+          <t>86882</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16276,12 +16276,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -16304,12 +16304,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>17218</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16319,12 +16319,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16339,12 +16339,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>11405</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16354,12 +16354,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16374,12 +16374,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10032</t>
+          <t>9861</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24111</t>
+          <t>23952</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16389,12 +16389,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -16534,12 +16534,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17050</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16549,12 +16549,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16569,12 +16569,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16584,12 +16584,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16604,12 +16604,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>13612</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29448</t>
+          <t>29190</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16619,12 +16619,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -16647,12 +16647,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>36840</t>
+          <t>36084</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -16662,49 +16662,49 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>29782</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>21379</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>41972</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
           <t>5,64%</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>29782</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>20977</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>40122</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
           <t>78</t>
@@ -16717,12 +16717,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>44293</t>
+          <t>43641</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>70621</t>
+          <t>71109</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -16732,12 +16732,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -16760,12 +16760,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>194500</t>
+          <t>195085</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>252684</t>
+          <t>253087</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16775,12 +16775,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16795,12 +16795,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>222523</t>
+          <t>223734</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>280782</t>
+          <t>278655</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16810,12 +16810,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16830,12 +16830,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>433500</t>
+          <t>437639</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>514304</t>
+          <t>523506</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16845,12 +16845,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>37,45%</t>
         </is>
       </c>
     </row>
@@ -16873,12 +16873,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>178436</t>
+          <t>178506</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>230152</t>
+          <t>230921</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -16888,12 +16888,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -16908,12 +16908,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>250983</t>
+          <t>250233</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>300081</t>
+          <t>301636</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -16923,12 +16923,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -16943,12 +16943,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>444499</t>
+          <t>445507</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>516073</t>
+          <t>521974</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -16958,12 +16958,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -16986,12 +16986,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>120588</t>
+          <t>120837</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>228412</t>
+          <t>221461</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17001,12 +17001,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17021,12 +17021,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>136564</t>
+          <t>136757</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>178280</t>
+          <t>180842</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17036,12 +17036,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17056,12 +17056,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>272272</t>
+          <t>271896</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>381281</t>
+          <t>373140</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17071,12 +17071,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -17099,12 +17099,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>22739</t>
+          <t>22566</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>40772</t>
+          <t>40634</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17134,12 +17134,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17931</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>35229</t>
+          <t>35567</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17149,12 +17149,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17169,12 +17169,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>44384</t>
+          <t>44565</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>70628</t>
+          <t>69726</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17184,12 +17184,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
